--- a/media/exports/黄胜原_8718_任前联审.xlsx
+++ b/media/exports/黄胜原_8718_任前联审.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>☑</t>
+          <t>是 ☑  否 ☐</t>
         </is>
       </c>
       <c r="C6" s="43" t="n"/>
@@ -922,14 +922,14 @@
       <c r="G6" s="44" t="n"/>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>是 ☑  否 ☐</t>
         </is>
       </c>
       <c r="I6" s="43" t="n"/>
       <c r="J6" s="44" t="n"/>
       <c r="K6" s="16" t="inlineStr">
         <is>
-          <t>☑</t>
+          <t>是 ☑  否 ☐</t>
         </is>
       </c>
       <c r="L6" s="43" t="n"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>☑</t>
+          <t>是 ☑  否 ☐</t>
         </is>
       </c>
       <c r="C7" s="43" t="n"/>
@@ -959,14 +959,14 @@
       <c r="G7" s="44" t="n"/>
       <c r="H7" s="16" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>是 ☐  否 ☑</t>
         </is>
       </c>
       <c r="I7" s="43" t="n"/>
       <c r="J7" s="44" t="n"/>
       <c r="K7" s="16" t="inlineStr">
         <is>
-          <t>☑</t>
+          <t>是 ☑  否 ☐</t>
         </is>
       </c>
       <c r="L7" s="43" t="n"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>☑</t>
+          <t>是 ☑  否 ☐</t>
         </is>
       </c>
       <c r="C8" s="43" t="n"/>
@@ -995,12 +995,16 @@
       <c r="E8" s="43" t="n"/>
       <c r="F8" s="43" t="n"/>
       <c r="G8" s="44" t="n"/>
-      <c r="H8" s="16" t="inlineStr"/>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>是 ☐  否 ☐</t>
+        </is>
+      </c>
       <c r="I8" s="43" t="n"/>
       <c r="J8" s="44" t="n"/>
       <c r="K8" s="16" t="inlineStr">
         <is>
-          <t>☑</t>
+          <t>是 ☑  否 ☐</t>
         </is>
       </c>
       <c r="L8" s="43" t="n"/>
@@ -1137,7 +1141,7 @@
       <c r="C12" s="44" t="n"/>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>☑</t>
+          <t>是 ☑  否 ☐</t>
         </is>
       </c>
       <c r="E12" s="43" t="n"/>
@@ -1154,7 +1158,7 @@
       <c r="K12" s="44" t="n"/>
       <c r="L12" s="16" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>是 ☐  否 ☑</t>
         </is>
       </c>
       <c r="M12" s="43" t="n"/>
@@ -1281,7 +1285,7 @@
       <c r="B17" s="48" t="n"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D17" s="43" t="n"/>
